--- a/public/samples/ja/sample-group.xlsx
+++ b/public/samples/ja/sample-group.xlsx
@@ -113,7 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -155,11 +157,12 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +606,7 @@
       <c r="H3" s="3">
         <v>1</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="4">
         <v>8.9</v>
       </c>
     </row>
@@ -623,7 +626,7 @@
       <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="4">
         <v>8.5</v>
       </c>
     </row>
@@ -646,7 +649,7 @@
       <c r="H5" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="4">
         <v>9.9</v>
       </c>
     </row>
@@ -666,7 +669,7 @@
       <c r="H6" s="3">
         <v>2</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="4">
         <v>9</v>
       </c>
     </row>
@@ -686,7 +689,7 @@
       <c r="H7" s="3">
         <v>3</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="4">
         <v>10.1</v>
       </c>
     </row>
@@ -703,7 +706,7 @@
       <c r="H8" s="3">
         <v>3</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="4">
         <v>9.3</v>
       </c>
     </row>
@@ -720,7 +723,7 @@
       <c r="H9" s="3">
         <v>4</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="4">
         <v>8.9</v>
       </c>
     </row>
@@ -737,7 +740,7 @@
       <c r="H10" s="3">
         <v>4</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="4">
         <v>8.5</v>
       </c>
     </row>
@@ -760,7 +763,7 @@
       <c r="H11" s="3">
         <v>5</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="4">
         <v>10</v>
       </c>
     </row>
@@ -780,7 +783,7 @@
       <c r="H12" s="3">
         <v>5</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="4">
         <v>9.5</v>
       </c>
     </row>
@@ -800,7 +803,7 @@
       <c r="H13" s="3">
         <v>1</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="4">
         <v>9.1</v>
       </c>
     </row>
@@ -817,7 +820,7 @@
       <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="4">
         <v>9.1</v>
       </c>
     </row>
@@ -834,7 +837,7 @@
       <c r="H15" s="3">
         <v>1</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="4">
         <v>8.5</v>
       </c>
     </row>
@@ -854,7 +857,7 @@
       <c r="H16" s="3">
         <v>2</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="4">
         <v>10.1</v>
       </c>
     </row>
@@ -871,7 +874,7 @@
       <c r="H17" s="3">
         <v>2</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="4">
         <v>9.3</v>
       </c>
     </row>
@@ -891,7 +894,7 @@
       <c r="H18" s="3">
         <v>2</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="4">
         <v>8.6</v>
       </c>
     </row>
@@ -914,7 +917,7 @@
       <c r="H19" s="3">
         <v>3</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="4">
         <v>10</v>
       </c>
     </row>
@@ -934,7 +937,7 @@
       <c r="H20" s="3">
         <v>3</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="4">
         <v>9</v>
       </c>
     </row>
@@ -951,7 +954,7 @@
       <c r="H21" s="3">
         <v>3</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="4">
         <v>9.5</v>
       </c>
     </row>
@@ -971,7 +974,7 @@
       <c r="H22" s="3">
         <v>4</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="4">
         <v>9.7</v>
       </c>
     </row>
@@ -991,7 +994,7 @@
       <c r="H23" s="3">
         <v>4</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="4">
         <v>9.4</v>
       </c>
     </row>
@@ -1008,7 +1011,7 @@
       <c r="H24" s="3">
         <v>4</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="4">
         <v>9.7</v>
       </c>
     </row>
@@ -1025,7 +1028,7 @@
       <c r="H25" s="3">
         <v>5</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="4">
         <v>9.8</v>
       </c>
     </row>
@@ -1045,7 +1048,7 @@
       <c r="H26" s="3">
         <v>5</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="4">
         <v>8.3</v>
       </c>
     </row>
@@ -1068,7 +1071,7 @@
       <c r="H27" s="3">
         <v>5</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="4">
         <v>8.6</v>
       </c>
     </row>
@@ -1088,7 +1091,7 @@
       <c r="H28" s="3">
         <v>6</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="4">
         <v>9.5</v>
       </c>
     </row>
@@ -1108,7 +1111,7 @@
       <c r="H29" s="3">
         <v>6</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="4">
         <v>9.4</v>
       </c>
     </row>
@@ -1125,7 +1128,7 @@
       <c r="H30" s="3">
         <v>6</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="4">
         <v>9.3</v>
       </c>
     </row>
@@ -1148,7 +1151,7 @@
       <c r="H31" s="3">
         <v>6</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="4">
         <v>9.5</v>
       </c>
     </row>
@@ -1168,7 +1171,7 @@
       <c r="H32" s="3">
         <v>6</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="4">
         <v>8.4</v>
       </c>
     </row>

--- a/public/samples/ja/sample-group.xlsx
+++ b/public/samples/ja/sample-group.xlsx
@@ -566,7 +566,7 @@
         <v>名前</v>
       </c>
       <c r="C2" s="3" t="str">
-        <v>性別♀</v>
+        <v>性別</v>
       </c>
       <c r="D2" s="3" t="str">
         <v>走力</v>
@@ -595,7 +595,7 @@
         <v>田中 綾香</v>
       </c>
       <c r="C3" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D3" s="3" t="str">
         <v>○</v>
@@ -617,6 +617,9 @@
       <c r="B4" s="3" t="str">
         <v>山本 武志</v>
       </c>
+      <c r="C4" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D4" s="3" t="str">
         <v>○</v>
       </c>
@@ -638,7 +641,7 @@
         <v>鈴木 美里</v>
       </c>
       <c r="C5" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E5" s="3" t="str">
         <v>○</v>
@@ -661,7 +664,7 @@
         <v>佐藤 可奈子</v>
       </c>
       <c r="C6" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -680,6 +683,9 @@
       <c r="B7" s="3" t="str">
         <v>伊藤 弘樹</v>
       </c>
+      <c r="C7" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F7" s="3" t="str">
         <v>○</v>
       </c>
@@ -700,6 +706,9 @@
       <c r="B8" s="3" t="str">
         <v>小林 優太</v>
       </c>
+      <c r="C8" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G8" s="3">
         <v>2</v>
       </c>
@@ -717,6 +726,9 @@
       <c r="B9" s="3" t="str">
         <v>中村 芽衣</v>
       </c>
+      <c r="C9" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G9" s="3">
         <v>3</v>
       </c>
@@ -734,6 +746,9 @@
       <c r="B10" s="3" t="str">
         <v>加藤 信次</v>
       </c>
+      <c r="C10" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
@@ -752,7 +767,7 @@
         <v>斉藤 まどか</v>
       </c>
       <c r="C11" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F11" s="3" t="str">
         <v>○</v>
@@ -774,6 +789,9 @@
       <c r="B12" s="3" t="str">
         <v>三浦 太一</v>
       </c>
+      <c r="C12" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D12" s="3" t="str">
         <v>○</v>
       </c>
@@ -795,7 +813,7 @@
         <v>高橋 直美</v>
       </c>
       <c r="C13" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -814,6 +832,9 @@
       <c r="B14" s="3" t="str">
         <v>林 健治</v>
       </c>
+      <c r="C14" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G14" s="3">
         <v>3</v>
       </c>
@@ -831,6 +852,9 @@
       <c r="B15" s="3" t="str">
         <v>渡辺 明良</v>
       </c>
+      <c r="C15" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G15" s="3">
         <v>2</v>
       </c>
@@ -848,6 +872,9 @@
       <c r="B16" s="3" t="str">
         <v>森田 愛</v>
       </c>
+      <c r="C16" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="E16" s="3" t="str">
         <v>○</v>
       </c>
@@ -868,6 +895,9 @@
       <c r="B17" s="3" t="str">
         <v>山田 孝史</v>
       </c>
+      <c r="C17" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G17" s="3">
         <v>1</v>
       </c>
@@ -886,7 +916,7 @@
         <v>井上 由貴</v>
       </c>
       <c r="C18" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -906,7 +936,7 @@
         <v>渋谷 理央</v>
       </c>
       <c r="C19" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F19" s="3" t="str">
         <v>○</v>
@@ -929,7 +959,7 @@
         <v>佐々木 春香</v>
       </c>
       <c r="C20" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -948,6 +978,9 @@
       <c r="B21" s="3" t="str">
         <v>高木 和也</v>
       </c>
+      <c r="C21" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
@@ -965,6 +998,9 @@
       <c r="B22" s="3" t="str">
         <v>田村 充</v>
       </c>
+      <c r="C22" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D22" s="3" t="str">
         <v>○</v>
       </c>
@@ -985,6 +1021,9 @@
       <c r="B23" s="3" t="str">
         <v>鈴木 亜莉斯</v>
       </c>
+      <c r="C23" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D23" s="3" t="str">
         <v>○</v>
       </c>
@@ -1005,6 +1044,9 @@
       <c r="B24" s="3" t="str">
         <v>田中 孝司</v>
       </c>
+      <c r="C24" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G24" s="3">
         <v>2</v>
       </c>
@@ -1022,6 +1064,9 @@
       <c r="B25" s="3" t="str">
         <v>山田 ジョン</v>
       </c>
+      <c r="C25" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G25" s="3">
         <v>2</v>
       </c>
@@ -1040,7 +1085,7 @@
         <v>佐藤 幸子</v>
       </c>
       <c r="C26" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G26" s="3">
         <v>1</v>
@@ -1060,7 +1105,7 @@
         <v>伊藤 花子</v>
       </c>
       <c r="C27" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D27" s="3" t="str">
         <v>○</v>
@@ -1082,6 +1127,9 @@
       <c r="B28" s="3" t="str">
         <v>小林 ジェイク</v>
       </c>
+      <c r="C28" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D28" s="3" t="str">
         <v>○</v>
       </c>
@@ -1103,7 +1151,7 @@
         <v>中村 未来</v>
       </c>
       <c r="C29" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G29" s="3">
         <v>2</v>
@@ -1122,6 +1170,9 @@
       <c r="B30" s="3" t="str">
         <v>加藤 琳</v>
       </c>
+      <c r="C30" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G30" s="3">
         <v>3</v>
       </c>
@@ -1140,7 +1191,7 @@
         <v>斉藤 恵里香</v>
       </c>
       <c r="C31" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D31" s="3" t="str">
         <v>○</v>
@@ -1161,6 +1212,9 @@
       </c>
       <c r="B32" s="3" t="str">
         <v>三浦 太郎</v>
+      </c>
+      <c r="C32" s="2" t="str">
+        <v>♂</v>
       </c>
       <c r="D32" s="3" t="str">
         <v>○</v>
